--- a/AAII_Financials/Quarterly/WCN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WCN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
   <si>
     <t>WCN</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2561600</v>
+      </c>
+      <c r="E8" s="3">
         <v>2370600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2373300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2458400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2407100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2228200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2260300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2338500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2248200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2072700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2035600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2064700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2021100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1900500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1869300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1879900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1816400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1646300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1624300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1597200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1533900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1395900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1398300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1389600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1305800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1352400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1362000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1412400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1369600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1244600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1261700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1281100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2380100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1140100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1157200</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1206500</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2266800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1091300</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1048600</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1084900</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1479200</v>
+      </c>
+      <c r="E9" s="3">
         <v>1361100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1364200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1406900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1392900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1291400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1324800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1344100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1301100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1221800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1195600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1204600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1197300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1146900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1138000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1120600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1087900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>989500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>980900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>946100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>901200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>825900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>846900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>828800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>785700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>815400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>814200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>835100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>815800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>733700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>746200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>737500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1387000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>660700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>680400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>695100</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1329300</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>643400</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>617900</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>636300</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1082400</v>
+      </c>
+      <c r="E10" s="3">
         <v>1009500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1009100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1051500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1014200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>936700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>935500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>994400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>947100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>850900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>840000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>860100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>823700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>753600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>731300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>759300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>728500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>656800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>643400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>651100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>632700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>570000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>551400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>560800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>520100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>537000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>547900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>577300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>553800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>510900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>515500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>543600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>993100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>479400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>476800</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>511400</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>937500</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>447900</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>430700</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>448600</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,252 +1496,261 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>67000</v>
+      </c>
+      <c r="E14" s="3">
         <v>74700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>5600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>25400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>6700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>15700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>118100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>10200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>11900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>6600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>66600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>33800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>3900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>5000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>23900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>7800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>6400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>33800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>118400</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>6100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>29400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>6100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>438300</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>2700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>33300</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>14000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>10100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>16900</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>17700</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-1700</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>12700</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>3400</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>15200</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>800</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>140500</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>141700</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>23000</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>7700</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>325900</v>
+      </c>
+      <c r="E15" s="3">
         <v>314700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>319200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>315300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>307700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>289900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>321800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>293600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>285400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>263000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>253100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>254400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>252400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>243300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>242800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>232100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>226400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>217600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>214200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>207300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>201900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>189600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>196700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>190200</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>183000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>182500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>188500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>189900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>188100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>177400</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>177200</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>175100</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>328200</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>159300</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>160600</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>163600</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>308300</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>150800</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>144200</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>152700</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2057100</v>
+      </c>
+      <c r="E17" s="3">
         <v>1926100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1946100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1985300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1940800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1820200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2339100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1853000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1807200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1696200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1796100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1649400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1643200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1581900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1557300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1553100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1486800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1372400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1375000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1427300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1267100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1157600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1201100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1158900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1538100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1135400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1167800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1175800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1147500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1059800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1061800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1048200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1980700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>951400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>982200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>987700</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2033500</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1064900</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>909500</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>926300</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>504500</v>
+      </c>
+      <c r="E18" s="3">
         <v>444500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>427200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>473100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>466200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>408000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-78800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>485500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>441000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>376400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>239500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>415400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>377900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>318600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>312000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>326800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>329600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>273900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>249300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>169900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>266800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>238300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>197200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>230700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-232300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>217000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>194200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>236600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>222100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>184800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>199900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>232900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>399400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>188700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>175000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>218800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>233300</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>26400</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>139100</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>158600</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,618 +2085,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-33300</v>
+      </c>
+      <c r="E20" s="3">
         <v>1600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-6400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-10100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>4300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-9600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>15800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>9500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-4600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-6900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>10700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>7400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>3300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>8200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>7100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-7700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>4200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-4600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>5200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>2300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>1000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>3500</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>1500</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>1700</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>800</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>1300</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>863700</v>
+      </c>
+      <c r="E21" s="3">
         <v>757600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>749300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>794900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>783900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>697700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>238400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>784100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>724000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>639900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>488300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>679300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>630100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>565200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>570600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>568500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>551300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>484600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>474200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>384600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>471900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>436100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>396400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>422500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-42300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>391800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>385600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>427100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>412200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>366400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>372500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>413200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>729900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>349000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>339100</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>383800</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>543300</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>178000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>284600</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>311700</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>91200</v>
+      </c>
+      <c r="E22" s="3">
         <v>87700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>86500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>84400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>82800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>80900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>82400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>83500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>82400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>78500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>69700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>69000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>67500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>68400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>76400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>50500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>42400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>37800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>47900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>44200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>45000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>46000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>42800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>40600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>40900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>37700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>35200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>35300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>35400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>35500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>29300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>35200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>63400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>32800</v>
-      </c>
-      <c r="AK22" s="3">
-        <v>32500</v>
       </c>
       <c r="AL22" s="3">
         <v>32500</v>
       </c>
       <c r="AM22" s="3">
+        <v>32500</v>
+      </c>
+      <c r="AN22" s="3">
         <v>60300</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>29100</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>27400</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>27600</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>383700</v>
+      </c>
+      <c r="E23" s="3">
         <v>283600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>341000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>374800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>389200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>313000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-281600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>400100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>356000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>288500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>161400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>292200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>277700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>252200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>251400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>285900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>282500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>229200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>212100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>133100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>225000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>200600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>156800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>191600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-266200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>171600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>161900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>201900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>188600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>153500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>166000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>202900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>338300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>156900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>146000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>187800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>174700</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>-1900</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>113000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>131400</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>87300</v>
+      </c>
+      <c r="E24" s="3">
         <v>64200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>82500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>88500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>98900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>71500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-85600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>92000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>80600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>59400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>34800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>63000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>68600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>54400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>57100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>48800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>58300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>48800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>45700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>18400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>47900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>40300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>26300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>33700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-38700</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>28700</v>
       </c>
       <c r="AC24" s="3">
         <v>28700</v>
       </c>
       <c r="AD24" s="3">
+        <v>28700</v>
+      </c>
+      <c r="AE24" s="3">
         <v>42800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>39800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>28000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>33200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>52100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>74400</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>31900</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>100700</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>64400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>35800</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>-16900</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>27300</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>42500</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>296400</v>
+      </c>
+      <c r="E26" s="3">
         <v>219300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>258500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>286300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>290300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>241500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-196000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>308000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>275400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>229100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>126600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>229200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>209200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>197800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>194300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>237100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>224200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>180400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>166400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>114700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>177100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>160300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>130600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>158000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-227500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>142900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>133200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>159100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>148800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>125600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>132800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>150800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>263800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>125000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>45300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>123400</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>138900</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>15000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>85700</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>88900</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>296400</v>
+      </c>
+      <c r="E27" s="3">
         <v>219300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>258500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>286300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>290300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>241500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-196000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>308000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>275500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>230100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>126800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>229000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>209200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>197800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>194400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>236900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>224100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>180300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>166300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>114400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>177000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>160300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>130700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>158000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-227100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>143000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>133300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>159100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>148800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>125600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>132700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>150800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>263600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>124900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>45300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>123200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>138500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>14900</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>85600</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>88600</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3224,8 +3285,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -3242,11 +3303,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-300</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
@@ -3254,11 +3315,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>269800</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>33300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>6400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>10100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-4300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>9600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-15800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-9500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>4600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>6900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-10700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-7400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-3300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-8200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-7100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>7700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-4200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>4600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-5200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-3500</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-800</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-1300</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>296400</v>
+      </c>
+      <c r="E33" s="3">
         <v>219300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>258500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>286300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>290300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>241500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-196000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>308000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>275500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>230100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>126800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>229000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>209200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>197800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>194400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>236900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>224100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>180300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>166300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>114400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>177000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>160300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>130700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>158000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-227100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>143000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>133300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>159100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>148800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>125600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>132500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>150800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>263600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>124900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>315100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>123200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>138500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>14900</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>85600</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>88600</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>296400</v>
+      </c>
+      <c r="E35" s="3">
         <v>219300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>258500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>286300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>290300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>241500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-196000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>308000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>275500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>230100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>126800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>229000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>209200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>197800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>194400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>236900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>224100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>180300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>166300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>114400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>177000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>160300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>130700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>158000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-227100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>143000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>133300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>159100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>148800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>125600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>132500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>150800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>263600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>124900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>315100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>123200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>138500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>14900</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>85600</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>88600</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,175 +4305,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>98200</v>
+      </c>
+      <c r="E41" s="3">
         <v>112400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>46000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>117600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>110200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>111200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>62400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>115300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>78700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>112000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>78400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>96200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>91700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>133900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>78600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>200200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>217800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>391400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>147400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>339500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>727400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>743500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>617300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>859100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>790600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1195300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>326700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>303800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>209200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>499500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>319300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>244400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>145800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>217500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>433800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>495300</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>399700</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>268500</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>154400</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>119300</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E42" s="3">
         <v>1800</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>2300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>5500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>7800</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>9700</v>
-      </c>
-      <c r="K42" s="3">
-        <v>18500</v>
       </c>
       <c r="L42" s="3">
         <v>18500</v>
       </c>
       <c r="M42" s="3">
+        <v>18500</v>
+      </c>
+      <c r="N42" s="3">
         <v>15800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>21200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>21000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>14900</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4463,141 +4553,147 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1069700</v>
+      </c>
+      <c r="E43" s="3">
         <v>1033100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1069500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1069600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1031900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>952000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>972600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>990900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>961500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>896700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>885100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>868100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>855500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>814700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>833900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>810900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>797900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>727700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>709600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>692100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>649600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>608800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>630300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>616600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>608800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>624400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>662800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>676700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>663900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>599400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>609500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>625000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>604100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>555300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>554500</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>588500</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>547700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>486400</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>485100</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>498300</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3">
         <v>78900</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>8</v>
@@ -4605,11 +4701,11 @@
       <c r="H44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3">
         <v>71200</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>8</v>
@@ -4617,11 +4713,11 @@
       <c r="L44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N44" s="3">
         <v>61700</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O44" s="3" t="s">
         <v>8</v>
@@ -4629,8 +4725,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4707,19 +4803,22 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3">
         <v>85600</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>8</v>
@@ -4727,11 +4826,11 @@
       <c r="H45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3">
         <v>80800</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>8</v>
@@ -4739,11 +4838,11 @@
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
         <v>74200</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>8</v>
@@ -4751,253 +4850,259 @@
       <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R45" s="3">
         <v>205100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>219200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>242100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>293600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>175700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>128800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>129500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>151800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>160700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>115700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>105600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>142600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>141100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>124800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>117500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>144000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>164100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>153600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>168500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>196800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>188600</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>109200</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>101800</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>122500</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>193000</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>167000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1399100</v>
+      </c>
+      <c r="E46" s="3">
         <v>1376300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1311600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1403600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1349700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1281000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1226900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1355100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1235700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1217100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1141800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1151700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1111700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1134300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1117600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1230300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1257700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1412800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1032800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1160300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1506400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1504000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1408300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1591400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1504900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1962200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1130600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1105300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>990600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1242900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1092900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1023100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>918400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>969600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1176900</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>1192900</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>1049200</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>877300</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>743400</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>784600</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="E47" s="3">
         <v>400</v>
       </c>
       <c r="F47" s="3">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="G47" s="3">
         <v>700</v>
       </c>
       <c r="H47" s="3">
+        <v>700</v>
+      </c>
+      <c r="I47" s="3">
         <v>1700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>7300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>8900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>17500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>15200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>9600</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
@@ -5073,252 +5178,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9280700</v>
+      </c>
+      <c r="E48" s="3">
         <v>9038100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9045800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8739000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8705700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8534500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8344100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8545900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8192300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8100700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7490100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7360300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7279100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7151700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7143400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6544200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6025300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5933300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5882500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5577400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5419400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5407300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5455400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5362400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5219800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5592800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5699600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>5564900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>5512600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>5319500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>5169000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>5069800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>5024900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>4924300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>4820900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>4783900</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>4729300</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>4721700</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>4738100</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>4773100</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10361600</v>
+      </c>
+      <c r="E49" s="3">
         <v>10374500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10398400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10279000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10282900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10123200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9942000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9905600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9599600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9474400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9007900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8931800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8652100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>8637800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>8576200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>8064100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>7858200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>7816500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>7538200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>7271300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>6921300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>6880000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>6881700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>6661800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>6640600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>6506000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>6673900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>6394600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>6440800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>6171100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>6361200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>5882400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>5858700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>5850500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>5769200</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>5797300</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>5673400</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>5627600</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>5457400</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>5515500</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>327400</v>
+      </c>
+      <c r="E52" s="3">
         <v>366600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>339600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>331300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>311000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>285600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>273200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>260700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>240400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>255600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>243100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>243500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>275900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>270100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>297300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>292000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>275100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>251900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>246400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>265900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>259100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>251600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>246900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>233800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>228700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>218400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>233600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>205500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>201800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>198500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>205100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>216900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>222600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>218800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>247700</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>136100</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>203500</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>242800</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>165100</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>114500</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>21399500</v>
+      </c>
+      <c r="E54" s="3">
         <v>21186400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>21129400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>20782500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>20678600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>20254500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>19817800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>20095400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>19301500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>19082700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>17915900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>17731200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>17359500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>17227100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>17134600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>16130700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>15416200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>15414400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>14699900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>14274800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>14106200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>14042900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>13992400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>13849400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>13594000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>14279400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>13737700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>13270200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>13145800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>12931900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>12627300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>12192100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>12024500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>11963200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>12014700</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>11910300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>11655400</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>11469400</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>11103900</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>11187700</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>771800</v>
+      </c>
+      <c r="E57" s="3">
         <v>712400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>765200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>759300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>729900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>625600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>637400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>706300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>663200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>589900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>642500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>604500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>539200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>526200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>638700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>507900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>496600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>423200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>392900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>341200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>326100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>280000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>290800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>403900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>367400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>398500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>437000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>428500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>408200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>339300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>360000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>331500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>343900</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>287900</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>330500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>277000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>239200</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>247700</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>251300</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>247300</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>83900</v>
+      </c>
+      <c r="E58" s="3">
         <v>63300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>67600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>65600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>65500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>62000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>63000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>62100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>64700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>67100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>73900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>81200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>58900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>65700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>6800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>6700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>6300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>44900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>22700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>21800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>23900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>105600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>25300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>21900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>23000</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>16400</v>
       </c>
       <c r="AC58" s="3">
         <v>16400</v>
       </c>
       <c r="AD58" s="3">
+        <v>16400</v>
+      </c>
+      <c r="AE58" s="3">
         <v>20900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>18800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>16800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>20300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>20800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>19700</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>20600</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>30900</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>36500</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>42100</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>42500</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>12600</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>42700</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>622100</v>
+      </c>
+      <c r="E59" s="3">
         <v>486800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>632100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>500600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>500200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>451600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>645000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>432900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>472900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>467300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>547300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>443500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>412500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>401100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>867200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>864100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>834600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>789600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>817100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>782300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>742300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>721200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>712500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>709700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>649000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>575200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>553800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>542400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>515900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>488100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>506600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>462900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>434100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>433600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>441200</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>506300</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>444200</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>435000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>428300</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>399300</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2128100</v>
+      </c>
+      <c r="E60" s="3">
         <v>2007500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2124300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2087600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2001200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1829500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1878800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1754000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1770500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1631500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1687900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1575700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1463500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1383200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1512600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1378700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1337600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1257600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1232700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1145300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1092300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1106900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1028700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1135500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1039300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>990200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1007200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>991800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>942900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>844100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>886800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>815200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>797700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>742100</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>802600</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>819800</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>725400</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>725100</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>692200</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>689300</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9554700</v>
+      </c>
+      <c r="E61" s="3">
         <v>9372000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9078100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8891800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8616300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8655000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8345000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8436100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7966500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8044600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6963200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7043200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6906000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7090900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6890100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>6212000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5633500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5817600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5040500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4869200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4762900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4613600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4708700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4680200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4694700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5160700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>4353800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>4039400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>4082900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>4157100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>4153500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>3747200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>3792800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>3878700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>3899600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>3925800</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>3963900</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>3946200</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>3616800</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>3662000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>674000</v>
+      </c>
+      <c r="E62" s="3">
         <v>635800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>596000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>641900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>672000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>744200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>775200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>544400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>512700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>563000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>544500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>472700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>481600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>472900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1618200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1596700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1575500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1580000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1433100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1377200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1382500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1380600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1391600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1367600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1363600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1441400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1438300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1442700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1412200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1362000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1126800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1124500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1087400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1061600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1038400</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1170900</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>1158100</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>1144900</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>1140100</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>1215100</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>13478200</v>
+      </c>
+      <c r="E66" s="3">
         <v>13128700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>12884000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>12689100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>12325000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>12240300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>11957500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>11833900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11318300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>11291700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10218100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10139900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9900100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9988100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>10025900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>9192300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8551400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>8660000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7711000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>7396200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>7241800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>7105200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>7133100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>7187500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>7101900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>7597000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6804200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6479300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6443400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6368800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>6172700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>5692500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>5683500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>5687900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>5746000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>5921800</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>5855100</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>5823700</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>5456400</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>5573600</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5538400</v>
+      </c>
+      <c r="E72" s="3">
         <v>5330400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5199800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>5031100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4825800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4617000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4457000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4734000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4500000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4298200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4141700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4088700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3925400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3781500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3649500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3520400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>3342400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3177800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3056800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2950000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2889000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2765400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2659000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2582300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2473300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2749200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2654200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2569700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2452700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2346000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2264500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2174100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>2060200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1961300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>1856900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>1578600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>1487200</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>1395300</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>1413500</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>1359400</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7921200</v>
+      </c>
+      <c r="E76" s="3">
         <v>8057600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8245400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8093400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8353700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8014200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7860400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8261500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7983200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7786900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7692800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7586200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7454500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7234000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7108700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6938400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6864900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>6754400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>6988900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>6878700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>6864400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>6937700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>6859300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6661900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6492100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6682400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6933500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6791000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6702400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6563100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6454600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6499600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>6341000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>6275300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>6268700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>5988500</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>5800200</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>5645700</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>5647500</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>5614100</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>296400</v>
+      </c>
+      <c r="E81" s="3">
         <v>219300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>258500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>286300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>290300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>241500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-196000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>308000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>275500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>230100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>126800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>229000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>209200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>197800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>194400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>236900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>224100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>180300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>166300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>114400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>177000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>160300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>130700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>158000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-227100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>143000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>133300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>159100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>148800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>125600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>132500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>150800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>263600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>124900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>315100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>123200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>138500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>14900</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>85600</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>88600</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>257400</v>
+      </c>
+      <c r="E83" s="3">
         <v>242300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>261600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>248500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>241200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>222700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>213300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>215000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>213300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>204100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>201100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>193300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>188900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>180000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>242800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>232100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>226400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>217600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>214200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>207300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>201900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>189600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>196700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>190200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>183000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>182500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>188500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>189900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>188100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>177400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>177200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>175100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>328200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>159300</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>160600</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>163600</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>308300</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>150800</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>144200</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>152700</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>733300</v>
+      </c>
+      <c r="E89" s="3">
         <v>545600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>556900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>677400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>638200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>541500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>568900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>558300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>611400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>490300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>555900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>554200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>574400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>442400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>522400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>526500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>532800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>440900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>428300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>421500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>448100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>400400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>222900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>432400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>383600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>369600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>355100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>432400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>389300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>363800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>373400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>373000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>665000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>307300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>298800</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>336700</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>551600</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>287500</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>256400</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>279200</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-302400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-296600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-399400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-297200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-285300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-212500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-396700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-272100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-217200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-170000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-318400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-221400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-218400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-175800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-294400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-246900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-219100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-152300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-264800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-208100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-174600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-96800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-50400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>121300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-137800</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
-      </c>
       <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
         <v>222100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-139600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-114200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-172600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-171800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-201700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-91200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-161900</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-114800</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-202600</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-182400</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-139800</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-92800</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-606300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-355700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-589300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-413900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-416800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-603200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-513400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-851700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-459500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1334600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-395500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-581000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-286900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-317800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1228600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-966600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-402100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-489900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-658600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-702000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-232200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-100600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-396000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-290100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-226300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-133600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-540300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-245400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-512200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-128000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-501400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-185200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-685200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-402300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-177400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-155600</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-528000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-412900</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-143300</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-95100</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,58 +10455,59 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>88400</v>
+      </c>
+      <c r="E96" s="3">
         <v>88700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>89900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>81000</v>
-      </c>
-      <c r="G96" s="3">
-        <v>81500</v>
       </c>
       <c r="H96" s="3">
         <v>81500</v>
       </c>
       <c r="I96" s="3">
+        <v>81500</v>
+      </c>
+      <c r="J96" s="3">
         <v>81000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>74000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>73700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>73600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>73800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>65700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>65400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>65800</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-65300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-58900</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-59400</v>
       </c>
       <c r="T96" s="3">
         <v>-59400</v>
@@ -10282,31 +10516,31 @@
         <v>-59400</v>
       </c>
       <c r="V96" s="3">
-        <v>-53400</v>
+        <v>-59400</v>
       </c>
       <c r="W96" s="3">
         <v>-53400</v>
       </c>
       <c r="X96" s="3">
+        <v>-53400</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-53900</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-54000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-49000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-48900</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-48000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-48700</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-42100</v>
       </c>
       <c r="AE96" s="3">
         <v>-42100</v>
@@ -10318,34 +10552,37 @@
         <v>-42100</v>
       </c>
       <c r="AH96" s="3">
+        <v>-42100</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-36900</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-73600</v>
-      </c>
-      <c r="AJ96" s="3">
-        <v>-36800</v>
       </c>
       <c r="AK96" s="3">
         <v>-36800</v>
       </c>
       <c r="AL96" s="3">
+        <v>-36800</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-31700</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-63500</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-31700</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-31500</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-25400</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-186400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-96100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-28500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-239000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-205900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>113400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-95400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>338500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-176600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>878500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-177900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>22700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-323900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-65400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>578000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>425300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-266900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>292100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-7900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-98400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-227700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-165500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-74100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-71600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-559900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>627400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>212100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-84800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-168100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-55200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>208100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-86300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-309400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-167000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-78400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-85900</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>221100</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>239400</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-77900</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-120100</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>2400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-2500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>5900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ101" s="3">
-        <v>0</v>
-      </c>
       <c r="AK101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL101" s="3">
         <v>800</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>300</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>700</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>100</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-100</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-61100</v>
+      </c>
+      <c r="E102" s="3">
         <v>93100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-61000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>23100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>18000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>51300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-40300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>46100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-25300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>33600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-15000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-5300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-36200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>59100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-127000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-16200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-138700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>243700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-238800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-379400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-11400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>134800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-241200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>72200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-400800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>861000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>27400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>102100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-290900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>180700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>79400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>101900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-330600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-261900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>43900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>95500</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>245400</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>114100</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>35000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>63700</v>
       </c>
     </row>
